--- a/grupos/3BLCM - Estadisticos 20211.xlsx
+++ b/grupos/3BLCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="158">
   <si>
     <t>Materia</t>
   </si>
@@ -188,24 +188,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Camarillo Aburto Raymundo</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
+    <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -218,6 +218,24 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ARIZBET</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
     <t>ALTAMIRANO</t>
   </si>
   <si>
@@ -233,13 +251,37 @@
     <t>CARAZA</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
   </si>
   <si>
     <t>MALDONADO</t>
@@ -251,15 +293,30 @@
     <t>MORENO</t>
   </si>
   <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>XOCUA</t>
   </si>
   <si>
@@ -272,22 +329,31 @@
     <t>OSORIO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SORIA</t>
+    <t>CANSINO</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
   </si>
   <si>
     <t>CERON</t>
   </si>
   <si>
+    <t>PRADO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
   </si>
   <si>
     <t>SERRANO</t>
@@ -299,12 +365,33 @@
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>ROBRES</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>ARENZANO</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
@@ -323,21 +410,45 @@
     <t>JARED URIEL</t>
   </si>
   <si>
-    <t>ARIZBET</t>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>VALERIA ANGELY</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>SIARI DANAHY</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
   </si>
   <si>
     <t>YAMILE</t>
   </si>
   <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
     <t>ARIADNA</t>
   </si>
   <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>IKER</t>
+  </si>
+  <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
     <t>IVONNE SHERLINE</t>
   </si>
   <si>
@@ -347,151 +458,40 @@
     <t>NAHOMY</t>
   </si>
   <si>
+    <t>RITA ALEJANDRA</t>
+  </si>
+  <si>
     <t>MARIANA</t>
   </si>
   <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
     <t>ARANTZA</t>
   </si>
   <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>MARIA XIMENA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
     <t>JOSELIN GUADALUPE</t>
   </si>
   <si>
+    <t>ANEL</t>
+  </si>
+  <si>
     <t>LAURA IVETTE</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>CANSINO</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ROBRES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>ARENZANO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>SIARI DANAHY</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>IKER</t>
-  </si>
-  <si>
-    <t>RITA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>MARIA XIMENA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>ANEL</t>
   </si>
 </sst>
 </file>
@@ -989,25 +989,25 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1031,22 +1031,22 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>7</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1069,25 +1069,25 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1108,7 +1108,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1117,13 +1117,13 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1143,28 +1143,28 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1185,19 +1185,19 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>5</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1220,28 +1220,28 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1262,19 +1262,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>5</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1303,7 +1303,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1312,13 +1312,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1348,10 +1348,10 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1374,13 +1374,13 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>-1</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1389,10 +1389,10 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1416,7 +1416,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>5</v>
@@ -1425,10 +1425,10 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>-1</v>
@@ -1454,25 +1454,25 @@
         <v>9</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1493,22 +1493,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>10</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1534,22 +1534,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1611,22 +1611,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1659,7 +1659,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1688,22 +1688,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1724,7 +1724,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1765,22 +1765,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1801,19 +1801,19 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>9</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1842,22 +1842,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1878,7 +1878,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1887,7 +1887,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1919,22 +1919,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1955,19 +1955,19 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>9</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1996,22 +1996,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2041,13 +2041,13 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2067,28 +2067,28 @@
         <v>6</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2109,7 +2109,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2118,10 +2118,10 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2144,13 +2144,13 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2159,13 +2159,13 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2186,7 +2186,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2195,13 +2195,13 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2227,7 +2227,7 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2236,13 +2236,13 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2263,7 +2263,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>6</v>
@@ -2272,13 +2272,13 @@
         <v>5</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2304,22 +2304,22 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2340,22 +2340,22 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>6</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2375,28 +2375,28 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2429,10 +2429,10 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2452,13 +2452,13 @@
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2467,13 +2467,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2503,13 +2503,13 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2523,31 +2523,31 @@
         <v>-1</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>-1</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2577,13 +2577,13 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2606,25 +2606,25 @@
         <v>5</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2660,7 +2660,7 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2683,28 +2683,28 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2734,13 +2734,13 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2766,22 +2766,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2802,7 +2802,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2814,10 +2814,10 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2837,28 +2837,28 @@
         <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2888,13 +2888,13 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2920,22 +2920,22 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2965,10 +2965,10 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -2997,22 +2997,22 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3039,10 +3039,10 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3068,25 +3068,25 @@
         <v>7</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3116,13 +3116,13 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3151,22 +3151,22 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3187,7 +3187,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -3196,13 +3196,13 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3228,22 +3228,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3273,7 +3273,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3305,7 +3305,7 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3314,13 +3314,13 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3341,7 +3341,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>6</v>
@@ -3356,7 +3356,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3382,19 +3382,19 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3430,7 +3430,7 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3453,28 +3453,28 @@
         <v>9</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G36">
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3495,19 +3495,19 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>7</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3536,22 +3536,22 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3572,19 +3572,19 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>9</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -3610,25 +3610,25 @@
         <v>9</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3649,13 +3649,13 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>9</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>9</v>
@@ -3664,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3729,19 +3729,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>48.57</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>51.43</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3761,30 +3761,30 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>28.57</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3793,30 +3793,30 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>62.86</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="G4">
-        <v>34.29</v>
+        <v>31.43</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3828,27 +3828,27 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>68.56999999999999</v>
       </c>
       <c r="G5">
-        <v>28.57</v>
+        <v>31.43</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -3857,30 +3857,30 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>88.56999999999999</v>
+      </c>
+      <c r="G6">
+        <v>11.43</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>77.14</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>22.86</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -3889,25 +3889,25 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>77.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>2.86</v>
+        <v>5.71</v>
       </c>
     </row>
   </sheetData>
@@ -3917,7 +3917,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3946,39 +3946,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920283</v>
+        <v>20330051920288</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920284</v>
+        <v>20330051920302</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -3986,462 +3986,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920285</v>
+        <v>20330051920302</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920286</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920286</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920390</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920288</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920288</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920295</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920297</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920301</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920301</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920302</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920302</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920302</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920302</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920302</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920303</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330061460416</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920208</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920307</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920307</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920310</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" t="s">
-        <v>110</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920313</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920316</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4480,299 +4040,299 @@
         <v>20330051920302</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920286</v>
+        <v>20330051920288</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920288</v>
+        <v>20330051920283</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920301</v>
+        <v>20330051920284</v>
       </c>
       <c r="B5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920307</v>
+        <v>20330051920285</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920283</v>
+        <v>20330051920286</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920284</v>
+        <v>20330051920390</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920285</v>
+        <v>20330051920287</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920390</v>
+        <v>20330051920290</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920295</v>
+        <v>20330051920292</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920297</v>
+        <v>20330051920293</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920303</v>
+        <v>20330051920294</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330061460416</v>
+        <v>20330051920394</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920208</v>
+        <v>20330051920295</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920310</v>
+        <v>20330051920296</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920313</v>
+        <v>20330051920297</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920316</v>
+        <v>20330051920298</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920287</v>
+        <v>20330051920299</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4783,13 +4343,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920290</v>
+        <v>20330051920300</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4800,13 +4360,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920292</v>
+        <v>20330051920301</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4817,13 +4377,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920293</v>
+        <v>20330051920303</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4834,13 +4394,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920294</v>
+        <v>19330061460416</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4851,13 +4411,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920394</v>
+        <v>19330051920208</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -4868,13 +4428,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920296</v>
+        <v>20330051920304</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -4885,13 +4445,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920298</v>
+        <v>20330051920307</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -4902,13 +4462,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920299</v>
+        <v>20330051920308</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -4919,13 +4479,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920300</v>
+        <v>20330051920309</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -4936,13 +4496,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920304</v>
+        <v>20330051920310</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -4953,13 +4513,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920308</v>
+        <v>20330051920311</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -4970,13 +4530,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920309</v>
+        <v>20330051920216</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>152</v>
@@ -4987,13 +4547,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920311</v>
+        <v>20330051920312</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>153</v>
@@ -5004,13 +4564,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920216</v>
+        <v>20330051920379</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>154</v>
@@ -5021,13 +4581,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920312</v>
+        <v>20330051920313</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>155</v>
@@ -5038,13 +4598,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920379</v>
+        <v>20330051920314</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -5055,13 +4615,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920314</v>
+        <v>20330051920316</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
         <v>157</v>
@@ -5112,19 +4672,19 @@
         <v>20330051920284</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5135,42 +4695,42 @@
         <v>20330051920284</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920295</v>
+        <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5178,45 +4738,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920295</v>
+        <v>20330051920285</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920311</v>
+        <v>20330051920296</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5224,22 +4784,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920311</v>
+        <v>20330051920296</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5247,65 +4807,65 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920283</v>
+        <v>20330051920297</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920390</v>
+        <v>20330051920297</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920298</v>
+        <v>20330051920286</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
@@ -5316,22 +4876,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920299</v>
+        <v>20330051920295</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5339,19 +4899,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920309</v>
+        <v>20330051920298</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
@@ -5362,48 +4922,48 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920313</v>
+        <v>20330051920309</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920316</v>
+        <v>20330051920311</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3BLCM - Estadisticos 20211.xlsx
+++ b/grupos/3BLCM - Estadisticos 20211.xlsx
@@ -191,13 +191,13 @@
     <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Camarillo Aburto Raymundo</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Camarillo Aburto Raymundo</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
@@ -998,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -1075,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>9</v>
@@ -1111,7 +1111,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1229,7 +1229,7 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1342,7 +1342,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1383,7 +1383,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -1537,7 +1537,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -1573,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1614,7 +1614,7 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>8</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1691,7 +1691,7 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -1768,7 +1768,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -1804,7 +1804,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1845,7 +1845,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1881,7 +1881,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1922,7 +1922,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>10</v>
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -2076,7 +2076,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>7</v>
@@ -2153,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2189,7 +2189,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2230,7 +2230,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2266,7 +2266,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2307,7 +2307,7 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -2343,7 +2343,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2384,7 +2384,7 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -2420,7 +2420,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2461,7 +2461,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2520,7 +2520,7 @@
         <v>5</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -2538,7 +2538,7 @@
         <v>4</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -2574,7 +2574,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2615,7 +2615,7 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>4</v>
@@ -2692,7 +2692,7 @@
         <v>4</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>4</v>
@@ -2769,7 +2769,7 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
         <v>10</v>
@@ -2805,7 +2805,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2846,7 +2846,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -2923,7 +2923,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>10</v>
@@ -3000,7 +3000,7 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>7</v>
@@ -3077,7 +3077,7 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>4</v>
@@ -3154,7 +3154,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>6</v>
@@ -3231,7 +3231,7 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>10</v>
@@ -3308,7 +3308,7 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3385,7 +3385,7 @@
         <v>5</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>4</v>
@@ -3462,7 +3462,7 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>8</v>
@@ -3539,7 +3539,7 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>8</v>
@@ -3575,7 +3575,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>9</v>
@@ -3616,7 +3616,7 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>9</v>
@@ -3652,7 +3652,7 @@
         <v>9</v>
       </c>
       <c r="U38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3764,27 +3764,27 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>68.56999999999999</v>
       </c>
       <c r="G3">
-        <v>28.57</v>
+        <v>31.43</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3805,7 +3805,7 @@
         <v>31.43</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3816,7 +3816,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3825,19 +3825,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>68.56999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G5">
-        <v>31.43</v>
+        <v>28.57</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3917,7 +3917,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3978,29 +3978,9 @@
         <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920302</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4037,33 +4017,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920302</v>
+        <v>20330051920288</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920288</v>
+        <v>20330051920302</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4637,7 +4617,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4669,22 +4649,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920284</v>
+        <v>20330051920285</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4692,22 +4672,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920284</v>
+        <v>20330051920285</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4715,22 +4695,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920285</v>
+        <v>20330051920287</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4738,22 +4718,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920285</v>
+        <v>20330051920287</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4776,7 +4756,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4845,7 +4825,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4853,22 +4833,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920286</v>
+        <v>20330051920284</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4876,22 +4856,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920295</v>
+        <v>20330051920286</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4899,22 +4879,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920298</v>
+        <v>20330051920295</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4922,22 +4902,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920309</v>
+        <v>20330051920298</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4945,24 +4925,47 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>20330051920309</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
         <v>20330051920311</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>95</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>95</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>151</v>
       </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
         <v>56</v>
       </c>
-      <c r="G14">
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20211.xlsx
+++ b/grupos/3BLCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="158">
   <si>
     <t>Materia</t>
   </si>
@@ -188,18 +188,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Camarillo Aburto Raymundo</t>
+  </si>
+  <si>
     <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Camarillo Aburto Raymundo</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
@@ -218,235 +218,235 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>CARAZA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>CAMARILLO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MIRAFUENTES</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>SORIA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>CANSINO</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROBRES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ARENZANO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>KAREN ESTEPHANY</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>JARED URIEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>ARIZBET</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>VALERIA ANGELY</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>SIARI DANAHY</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>YAMILE</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>IKER</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
     <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>CARAZA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MIRAFUENTES</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>CANSINO</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROBRES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARENZANO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>KAREN ESTEPHANY</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>JARED URIEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>SIARI DANAHY</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>IKER</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
   </si>
   <si>
     <t>IVONNE SHERLINE</t>
@@ -1010,25 +1010,25 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -1037,16 +1037,16 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1090,28 +1090,28 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1167,40 +1167,40 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1244,40 +1244,40 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1309,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>7</v>
@@ -1321,40 +1321,40 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1377,7 +1377,7 @@
         <v>5</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -1386,7 +1386,7 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -1395,28 +1395,28 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>5</v>
@@ -1425,13 +1425,13 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1475,22 +1475,22 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1552,22 +1552,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1579,13 +1579,13 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1629,22 +1629,22 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1662,7 +1662,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1706,22 +1706,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1783,22 +1783,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1810,13 +1810,13 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1860,22 +1860,22 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1884,7 +1884,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1893,7 +1893,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1937,22 +1937,22 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1970,7 +1970,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2014,40 +2014,40 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2091,22 +2091,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -2121,7 +2121,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2156,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -2168,22 +2168,22 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2192,13 +2192,13 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2233,7 +2233,7 @@
         <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -2245,22 +2245,22 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2269,13 +2269,13 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2322,22 +2322,22 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2349,13 +2349,13 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2399,22 +2399,22 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2429,7 +2429,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2464,7 +2464,7 @@
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -2476,37 +2476,37 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>4</v>
@@ -2550,25 +2550,25 @@
         <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2586,7 +2586,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2627,25 +2627,25 @@
         <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>5</v>
@@ -2663,7 +2663,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2707,22 +2707,22 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2734,13 +2734,13 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2784,22 +2784,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2811,13 +2811,13 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2861,34 +2861,34 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>5</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2938,22 +2938,22 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2968,10 +2968,10 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3015,31 +3015,31 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>5</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3048,7 +3048,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3089,25 +3089,25 @@
         <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -3119,13 +3119,13 @@
         <v>5</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>5</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3169,40 +3169,40 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>7</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3246,22 +3246,22 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>8</v>
@@ -3323,31 +3323,31 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>6</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3397,25 +3397,25 @@
         <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
         <v>5</v>
@@ -3430,10 +3430,10 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3477,22 +3477,22 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3501,16 +3501,16 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>8</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3554,40 +3554,40 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
         <v>10</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>9</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3631,25 +3631,25 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>8</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3729,19 +3729,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>60</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>25.71</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3761,19 +3761,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>68.56999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G3">
-        <v>31.43</v>
+        <v>25.71</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3784,7 +3784,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3793,19 +3793,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>68.56999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G4">
-        <v>31.43</v>
+        <v>25.71</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3816,7 +3816,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3825,19 +3825,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>71.43000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="G5">
-        <v>28.57</v>
+        <v>22.86</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3857,19 +3857,19 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>88.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="G6">
-        <v>11.43</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3889,25 +3889,25 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>94.29000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>8.57</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3917,7 +3917,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3942,46 +3942,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920288</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920302</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4017,47 +3977,47 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920288</v>
+        <v>20330051920283</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920302</v>
+        <v>20330051920284</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920283</v>
+        <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
         <v>125</v>
@@ -4068,13 +4028,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920284</v>
+        <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
         <v>126</v>
@@ -4085,13 +4045,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920285</v>
+        <v>20330051920390</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
         <v>127</v>
@@ -4102,13 +4062,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920286</v>
+        <v>20330051920287</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>128</v>
@@ -4119,13 +4079,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920390</v>
+        <v>20330051920288</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>129</v>
@@ -4136,13 +4096,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920287</v>
+        <v>20330051920290</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>130</v>
@@ -4153,13 +4113,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920290</v>
+        <v>20330051920292</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>131</v>
@@ -4170,13 +4130,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920292</v>
+        <v>20330051920293</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
         <v>132</v>
@@ -4187,13 +4147,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920293</v>
+        <v>20330051920294</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -4204,13 +4164,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920294</v>
+        <v>20330051920394</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
         <v>134</v>
@@ -4221,13 +4181,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920394</v>
+        <v>20330051920295</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
         <v>135</v>
@@ -4238,13 +4198,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920295</v>
+        <v>20330051920296</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
         <v>136</v>
@@ -4255,13 +4215,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920296</v>
+        <v>20330051920297</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
@@ -4272,13 +4232,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920297</v>
+        <v>20330051920298</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -4289,13 +4249,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920298</v>
+        <v>20330051920299</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -4306,13 +4266,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920299</v>
+        <v>20330051920300</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4323,13 +4283,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920300</v>
+        <v>20330051920301</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4340,13 +4300,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920301</v>
+        <v>20330051920302</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4360,10 +4320,10 @@
         <v>20330051920303</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4377,10 +4337,10 @@
         <v>19330061460416</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4394,10 +4354,10 @@
         <v>19330051920208</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -4411,10 +4371,10 @@
         <v>20330051920304</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -4428,10 +4388,10 @@
         <v>20330051920307</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -4445,10 +4405,10 @@
         <v>20330051920308</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -4462,10 +4422,10 @@
         <v>20330051920309</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -4479,10 +4439,10 @@
         <v>20330051920310</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -4496,10 +4456,10 @@
         <v>20330051920311</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -4513,10 +4473,10 @@
         <v>20330051920216</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>152</v>
@@ -4530,10 +4490,10 @@
         <v>20330051920312</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
         <v>153</v>
@@ -4547,10 +4507,10 @@
         <v>20330051920379</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
         <v>154</v>
@@ -4564,10 +4524,10 @@
         <v>20330051920313</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
         <v>155</v>
@@ -4581,10 +4541,10 @@
         <v>20330051920314</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -4598,10 +4558,10 @@
         <v>20330051920316</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
         <v>157</v>
@@ -4617,7 +4577,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4649,22 +4609,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920285</v>
+        <v>20330051920307</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4672,22 +4632,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920285</v>
+        <v>20330051920307</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4695,19 +4655,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920287</v>
+        <v>20330051920296</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>58</v>
@@ -4718,254 +4678,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920287</v>
+        <v>20330051920309</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920296</v>
-      </c>
-      <c r="B6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920296</v>
-      </c>
-      <c r="B7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920297</v>
-      </c>
-      <c r="B8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920297</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920284</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920286</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920295</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920298</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920309</v>
-      </c>
-      <c r="B14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920311</v>
-      </c>
-      <c r="B15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20211.xlsx
+++ b/grupos/3BLCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="158">
   <si>
     <t>Materia</t>
   </si>
@@ -1046,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -3889,16 +3889,16 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G7">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -4577,7 +4577,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4609,22 +4609,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920307</v>
+        <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4632,16 +4632,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920307</v>
+        <v>20330051920286</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920296</v>
+        <v>20330051920307</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4678,24 +4678,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
+        <v>20330051920307</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920296</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
         <v>20330051920309</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>89</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>116</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D7" t="s">
         <v>149</v>
       </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
         <v>57</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>5</v>
       </c>
     </row>
